--- a/02_고전문헌_통합비교분석/3대침구서적_통합분석_경혈명_별명_증치_수혈고증.xlsx
+++ b/02_고전문헌_통합비교분석/3대침구서적_통합분석_경혈명_별명_증치_수혈고증.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>金門(김문)</t>
+          <t>金門(금문)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
